--- a/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-MortalityRates-GKS-1986-1987.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-MortalityRates-GKS-1986-1987.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A907D182-30CB-4C3D-ACAA-8DD60E25462D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422620D5-F462-4525-9441-680E011083DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14325" yWindow="4095" windowWidth="24555" windowHeight="12540" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comment" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="29">
   <si>
     <t>Коэффициенты смертности населения РСФСР в 1986-1987 гг.</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Госкомстат СССР, "Таблицы смертности и ожидаемой продолжительности жизни населения", 1989, стр. 237-239.</t>
   </si>
   <si>
-    <t>Значения qx</t>
-  </si>
-  <si>
     <t>возраст</t>
   </si>
   <si>
@@ -115,6 +112,15 @@
   </si>
   <si>
     <t>10-14</t>
+  </si>
+  <si>
+    <t>Внимание!!!</t>
+  </si>
+  <si>
+    <t>Значения qx относятся не к году в среднем,</t>
+  </si>
+  <si>
+    <t>а ко всей (пятилетней) корзине в целом.</t>
   </si>
 </sst>
 </file>
@@ -124,8 +130,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -153,10 +167,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,22 +452,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -463,187 +488,187 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD2D123-9299-4DB6-AB36-8E3C14E520BC}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>1.77E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>3.15E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>1.4300000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>9.3000000000000005E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>2.6800000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>1.8600000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>3.62E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>4.8199999999999996E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>5.7400000000000003E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>6.8300000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>9.2899999999999996E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>1.3270000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>1.9050000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>2.8029999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>4.0419999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>5.9720000000000002E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>9.5320000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.15140000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.23633000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.35842000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -657,187 +682,187 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B14135-B3AE-48E7-882D-923757B592A7}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>1.9380000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>2.1900000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>1.08E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>7.6000000000000004E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>6.7000000000000002E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>2.7599999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>2.2499999999999998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>6.9699999999999996E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>8.2400000000000008E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>1.069E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>2.1260000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>3.1460000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>4.6309999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>6.8210000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>9.2939999999999995E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.20316999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.29775000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.42531000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -852,187 +877,187 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D811FF7-7CE0-4439-8DD7-B14D6E508CF4}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>2.2280000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>2.3900000000000002E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>1.1900000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>8.8000000000000003E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>7.7999999999999999E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>3.5300000000000002E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>2.9299999999999999E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>6.4400000000000004E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>1.077E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>1.261E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>1.635E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>2.147E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>3.2140000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>4.7879999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>6.9409999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>0.10397000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>0.15382000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.20649000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.28022999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.38080999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.50939000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -1046,187 +1071,187 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0550738-8012-4383-82AA-B6333CC0B3CF}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>1.6330000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>1.99E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>9.7000000000000005E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>6.3000000000000003E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>5.5000000000000003E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>1.98E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>1.5499999999999999E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>2.5200000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>3.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>3.5699999999999998E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>4.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>7.0699999999999999E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>1.0869999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>1.6549999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>2.6100000000000002E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>4.0309999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>6.0359999999999997E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.10478</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.17229</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.26966000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.40212999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -1240,187 +1265,187 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF9D34C-507E-4F37-B515-D2C7A68CA94C}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>1.883E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>1.6900000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>8.4999999999999995E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>5.9000000000000003E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>5.4000000000000001E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>2.4199999999999998E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>2.0699999999999998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>4.0200000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>5.7400000000000003E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>6.6400000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>9.3699999999999999E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>1.9720000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>2.962E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>4.4630000000000003E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>6.7549999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>9.2520000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.14169999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.21490999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.31768000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.45306999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -1434,187 +1459,187 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8178F2DA-1DC1-44F8-9271-8F76A779A91C}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>2.1760000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>1.8600000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>9.3000000000000005E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>6.8000000000000005E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>6.3000000000000003E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>3.1099999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>2.7000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>5.94E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>8.8800000000000007E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>1.0019999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>1.95E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>2.9680000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>4.5019999999999998E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>6.7119999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>0.10363</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>0.15794</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.20957999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.28476000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.39151000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.53176999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -1628,187 +1653,187 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963F1E12-7949-4D15-94B0-7C4D878B5CC1}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>1.575E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>1.5100000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>7.7999999999999999E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>4.4999999999999999E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>1.6900000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>1.41E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>2.1900000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>2.65E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>3.0500000000000002E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>4.45E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>6.5399999999999998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>1.021E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>1.5689999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>2.5329999999999998E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>4.0079999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>5.9490000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.10943</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.18440999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.29024</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.43035000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -1822,187 +1847,187 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F8652C-DD21-4828-A8F9-C3930CE2AB5D}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>2.0670000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>3.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>1.64E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>9.7999999999999997E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>3.64E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>2.7299999999999998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>5.7800000000000004E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>1.146E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>1.4829999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>1.5429999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>1.9560000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>2.6839999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>3.6769999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>5.0310000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>6.9309999999999997E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>9.1700000000000004E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.12711</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.18204000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.26434000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.38138</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -2016,187 +2041,187 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEAC7D06-B917-4B83-92DD-638B04F42FFF}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>2.35E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>3.64E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>1.8400000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
         <v>1.3699999999999999E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>4.5500000000000002E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>1.737E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
         <v>2.3019999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>2.3259999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
         <v>2.904E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>5.6129999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2">
         <v>7.4660000000000004E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
         <v>0.10544000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>0.15026</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
         <v>0.19989000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>0.26740999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
         <v>0.35737000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
         <v>0.47126000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -2205,4 +2230,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>